--- a/users.xlsx
+++ b/users.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthik Gunasekaran\Desktop\loss_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthik Gunasekaran\Desktop\loss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92607AA3-D761-493D-8E8D-3708BEAB575B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A310B5-4564-4FF5-94E8-029D7FD66579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$373</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="399">
   <si>
     <t>email_id</t>
   </si>
@@ -49,9 +49,6 @@
     <t>mallikharjun@meesho.com</t>
   </si>
   <si>
-    <t>Manager</t>
-  </si>
-  <si>
     <t>joseph.cherian@meesho.com</t>
   </si>
   <si>
@@ -284,13 +281,952 @@
   </si>
   <si>
     <t>User</t>
+  </si>
+  <si>
+    <t>tushar.dongare@meesho.com</t>
+  </si>
+  <si>
+    <t>ajit.vedak@meesho.com</t>
+  </si>
+  <si>
+    <t>banit.roy@meesho.com</t>
+  </si>
+  <si>
+    <t>prince.shukla@meesho.com</t>
+  </si>
+  <si>
+    <t>dhirender.deswal@meesho.com</t>
+  </si>
+  <si>
+    <t>tushar.sharma@meesho.com</t>
+  </si>
+  <si>
+    <t>siddharth.chhibber@meesho.com</t>
+  </si>
+  <si>
+    <t>Suresh.behera@meesho.com</t>
+  </si>
+  <si>
+    <t>abhishek.mhamunkar@meesho.com</t>
+  </si>
+  <si>
+    <t>axendra.chouhan@meesho.com</t>
+  </si>
+  <si>
+    <t>deepak.pradhan@meesho.com</t>
+  </si>
+  <si>
+    <t>ashish.sharma2@meesho.com</t>
+  </si>
+  <si>
+    <t>rahul.mishra3@meesho.com</t>
+  </si>
+  <si>
+    <t>prince.sharma@meesho.com</t>
+  </si>
+  <si>
+    <t>keshav.jee@meesho.com</t>
+  </si>
+  <si>
+    <t>alan.martin@meesho.com</t>
+  </si>
+  <si>
+    <t>vishnu.mishra1@meesho.com</t>
+  </si>
+  <si>
+    <t>akshit.ahuja@meesho.com</t>
+  </si>
+  <si>
+    <t>suraj.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>suren.hazarika@meesho.com</t>
+  </si>
+  <si>
+    <t>anupam.bal@meesho.com</t>
+  </si>
+  <si>
+    <t>vikram.rathore1@meesho.com</t>
+  </si>
+  <si>
+    <t>indu.bala@meesho.com</t>
+  </si>
+  <si>
+    <t>suraj.chaturvedi1@meesho.com</t>
+  </si>
+  <si>
+    <t>sourav.mishra@meesho.com</t>
+  </si>
+  <si>
+    <t>mukesh.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>vaibhav.bhadake1@meesho.com</t>
+  </si>
+  <si>
+    <t>himanshu.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>nilesh.parbhane@meesho.com</t>
+  </si>
+  <si>
+    <t>rohit.kakade@meesho.com</t>
+  </si>
+  <si>
+    <t>pradip.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>navneet.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>mukesh.patil@meesho.com</t>
+  </si>
+  <si>
+    <t>pankaj.tripathi@meesho.com</t>
+  </si>
+  <si>
+    <t>Sudhir.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>santosh.soni@meesho.com</t>
+  </si>
+  <si>
+    <t>sandeep.kushwaha@meesho.com</t>
+  </si>
+  <si>
+    <t>kranti.chouhan@meesho.com</t>
+  </si>
+  <si>
+    <t>ranjit@meesho.com</t>
+  </si>
+  <si>
+    <t>suresh.kannan@meesho.com</t>
+  </si>
+  <si>
+    <t>ravi.pathak@meesho.com</t>
+  </si>
+  <si>
+    <t>navin.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>jatinderpreet.kaur@meesho.com</t>
+  </si>
+  <si>
+    <t>vijay.sharma1@meesho.com</t>
+  </si>
+  <si>
+    <t>lokhnade.prakash@meesho.com</t>
+  </si>
+  <si>
+    <t>awwab.kirme@meesho.com</t>
+  </si>
+  <si>
+    <t>amar.pansare@meesho.com</t>
+  </si>
+  <si>
+    <t>deepak.sharma3@meesho.com</t>
+  </si>
+  <si>
+    <t>chandan.goswami@meesho.com</t>
+  </si>
+  <si>
+    <t>puspadhwaja.hans@meesho.com</t>
+  </si>
+  <si>
+    <t>surya.pratap@meesho.com</t>
+  </si>
+  <si>
+    <t>ashish.kumar4@meesho.com</t>
+  </si>
+  <si>
+    <t>Kuldeep.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>bajendra.rauta@meesho.com</t>
+  </si>
+  <si>
+    <t>rohit.dubey@meesho.com</t>
+  </si>
+  <si>
+    <t>sombir@meesho.com</t>
+  </si>
+  <si>
+    <t>rajesh.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>satrughan.chourasia@meesho.com</t>
+  </si>
+  <si>
+    <t>deepjyoti.talukdar@meesho.com</t>
+  </si>
+  <si>
+    <t>surya.das@meesho.com</t>
+  </si>
+  <si>
+    <t>indu@meesho.com</t>
+  </si>
+  <si>
+    <t>barun.santra@meesho.com</t>
+  </si>
+  <si>
+    <t>gaurav.tayade@meesho.com</t>
+  </si>
+  <si>
+    <t>dushyant.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>piyush.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>sonu.bairwa@meesho.com</t>
+  </si>
+  <si>
+    <t>sourabh.sain@meesho.com</t>
+  </si>
+  <si>
+    <t>amrendra.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>pritam.ghosh@meesho.com</t>
+  </si>
+  <si>
+    <t>aman.mishra@meesho.com</t>
+  </si>
+  <si>
+    <t>ramnaresh.dwivedi@meesho.com</t>
+  </si>
+  <si>
+    <t>arwinder.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>arun.prasher@meesho.com</t>
+  </si>
+  <si>
+    <t>bhupender@meesho.com</t>
+  </si>
+  <si>
+    <t>vivek.kaware@meesho.com</t>
+  </si>
+  <si>
+    <t>ravi.ranjan1@meesho.com</t>
+  </si>
+  <si>
+    <t>sudeep.pandey@meesho.com</t>
+  </si>
+  <si>
+    <t>kumar.sourav@meesho.com</t>
+  </si>
+  <si>
+    <t>debajit.nath@meesho.com</t>
+  </si>
+  <si>
+    <t>hirakjyoti.sarma@meesho.com</t>
+  </si>
+  <si>
+    <t>soubhik.sarkar@meesho.com</t>
+  </si>
+  <si>
+    <t>anuj.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>kishan.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>shubham.mishra2@meesho.com</t>
+  </si>
+  <si>
+    <t>shubham.kumar3@meesho.com</t>
+  </si>
+  <si>
+    <t>rahul.borude@meesho.com</t>
+  </si>
+  <si>
+    <t>jadav.kiran@meesho.com</t>
+  </si>
+  <si>
+    <t>akshaykumar.patel@meesho.com</t>
+  </si>
+  <si>
+    <t>tarun.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>mohd.juvair@meesho.com</t>
+  </si>
+  <si>
+    <t>adarsh.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>rakesh.kumar3@meesho.com</t>
+  </si>
+  <si>
+    <t>ramesh.hatile@meesho.com</t>
+  </si>
+  <si>
+    <t>samirul.sk@meesho.com</t>
+  </si>
+  <si>
+    <t>rekha.shinde@meesho.com</t>
+  </si>
+  <si>
+    <t>raj.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>arindam.dutta@meesho.com</t>
+  </si>
+  <si>
+    <t>vasiya.manjibhai@meesho.com</t>
+  </si>
+  <si>
+    <t>yash.singh2@meesho.com</t>
+  </si>
+  <si>
+    <t>mahaveer.sharma@meesho.com</t>
+  </si>
+  <si>
+    <t>ajay.kumar4@meesho.com</t>
+  </si>
+  <si>
+    <t>manish1@meesho.com</t>
+  </si>
+  <si>
+    <t>satyanarayana.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>jadav.kanaksinh@meesho.com</t>
+  </si>
+  <si>
+    <t>sandip.pandit@meesho.com</t>
+  </si>
+  <si>
+    <t>Akash.singh4@meesho.com</t>
+  </si>
+  <si>
+    <t>chavda.ashokbhai@meesho.com</t>
+  </si>
+  <si>
+    <t>ramavtar.mourya@meesho.com</t>
+  </si>
+  <si>
+    <t>sekhar.pandey@meesho.com</t>
+  </si>
+  <si>
+    <t>jay.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>sandipkumar.saravaiya@meesho.com</t>
+  </si>
+  <si>
+    <t>arvind.chauhan@meesho.com</t>
+  </si>
+  <si>
+    <t>pravin.mali@meesho.com</t>
+  </si>
+  <si>
+    <t>hemant.kumbharde@meesho.com</t>
+  </si>
+  <si>
+    <t>shubham.tiwari@meesho.com</t>
+  </si>
+  <si>
+    <t>kuldeep.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>karan.singh1@meesho.com</t>
+  </si>
+  <si>
+    <t>sunil@meesho.com</t>
+  </si>
+  <si>
+    <t>kuldeep.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>pawar.sunil@meesho.com</t>
+  </si>
+  <si>
+    <t>shriyansh.sen@meesho.com</t>
+  </si>
+  <si>
+    <t>Rajesh J</t>
+  </si>
+  <si>
+    <t>dipak.korde@meesho.com</t>
+  </si>
+  <si>
+    <t>Kanish@meesho.com</t>
+  </si>
+  <si>
+    <t>mayank.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>lavkush.tiwari@meesho.com</t>
+  </si>
+  <si>
+    <t>nitin.patil@meesho.com</t>
+  </si>
+  <si>
+    <t>mahaveer.kumawat@meesho.com</t>
+  </si>
+  <si>
+    <t>kamal1@meesho.com</t>
+  </si>
+  <si>
+    <t>krishan.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>aalok.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>raj.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>chunchun.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>lokesh.sharma1@meesho.com</t>
+  </si>
+  <si>
+    <t>rahulkumar.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>sushil.maharana@meesho.com</t>
+  </si>
+  <si>
+    <t>Rinku.Kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>kapil.gurjar@meesho.com</t>
+  </si>
+  <si>
+    <t>ravinder@meesho.com</t>
+  </si>
+  <si>
+    <t>devraj@meesho.com</t>
+  </si>
+  <si>
+    <t>amit.jadhav@meesho.com</t>
+  </si>
+  <si>
+    <t>mohit.sharma@meesho.com</t>
+  </si>
+  <si>
+    <t>sanjay.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>ankit.singh2@meesho.com</t>
+  </si>
+  <si>
+    <t>vipin.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>prodip.barman@meesho.com</t>
+  </si>
+  <si>
+    <t>kushal.sardar@meesho.com</t>
+  </si>
+  <si>
+    <t>sourav.purkait@meesho.com</t>
+  </si>
+  <si>
+    <t>pradip.bhoi@meesho.com</t>
+  </si>
+  <si>
+    <t>rohit.bhati@meesho.com</t>
+  </si>
+  <si>
+    <t>mohit.sharma1@meesho.com</t>
+  </si>
+  <si>
+    <t>rajneesh.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>trilochan@meesho.com</t>
+  </si>
+  <si>
+    <t>hemant.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>arun.shilpkar@meesho.com</t>
+  </si>
+  <si>
+    <t>hariom.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>shivam.soni@meesho.com</t>
+  </si>
+  <si>
+    <t>chandan.rana@meesho.com</t>
+  </si>
+  <si>
+    <t>shivraj.shekhawat@meesho.com</t>
+  </si>
+  <si>
+    <t>utkarsh.shukla1@meesho.com</t>
+  </si>
+  <si>
+    <t>mukul.goyal@meesho.com</t>
+  </si>
+  <si>
+    <t>uttekar.aditya@meesho.com</t>
+  </si>
+  <si>
+    <t>Suraj.kumar3@meesho.com</t>
+  </si>
+  <si>
+    <t>hemant.verma@meesho.com</t>
+  </si>
+  <si>
+    <t>praveen.malhotra@meesho.com</t>
+  </si>
+  <si>
+    <t>kamaljeet.kaur@meesho.com</t>
+  </si>
+  <si>
+    <t>nilesh.kshirsagar@meesho.com</t>
+  </si>
+  <si>
+    <t>naveen.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>ravi.karan@meesho.com</t>
+  </si>
+  <si>
+    <t>sonu.1@meesho.com</t>
+  </si>
+  <si>
+    <t>pandey.santosh@meesho.com</t>
+  </si>
+  <si>
+    <t>kalpesh.sangale@meesho.com</t>
+  </si>
+  <si>
+    <t>prakash.lonare@meesho.com</t>
+  </si>
+  <si>
+    <t>ajay.thakur@meesho.com</t>
+  </si>
+  <si>
+    <t>vikaskumar.ray@meesho.com</t>
+  </si>
+  <si>
+    <t>vishal.mistri@meesho.com</t>
+  </si>
+  <si>
+    <t>sagar.khaple@meesho.com</t>
+  </si>
+  <si>
+    <t>rahul.thakare@meesho.com</t>
+  </si>
+  <si>
+    <t>saurabhkumar.prashad@meesho.com</t>
+  </si>
+  <si>
+    <t>jamaluddin.khan@meesho.com</t>
+  </si>
+  <si>
+    <t>bibhuti.sethy@meesho.com</t>
+  </si>
+  <si>
+    <t>jasveer.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>pintoo.shah@meesho.com</t>
+  </si>
+  <si>
+    <t>arvind.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>Akshay.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>alok.anupam@meesho.com</t>
+  </si>
+  <si>
+    <t>brij.chauhan@meesho.com</t>
+  </si>
+  <si>
+    <t>bikash.borah@meesho.com</t>
+  </si>
+  <si>
+    <t>sonu.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>saikat.debnath@meesho.com</t>
+  </si>
+  <si>
+    <t>durgesh.kori@meesho.com</t>
+  </si>
+  <si>
+    <t>mantesh.bairwa@meesho.com</t>
+  </si>
+  <si>
+    <t>abdul.rahuf@meesho.com</t>
+  </si>
+  <si>
+    <t>rohit.shekhawat@meesho.com</t>
+  </si>
+  <si>
+    <t>gyan.jaiswal@meesho.com</t>
+  </si>
+  <si>
+    <t>rituraj.gupta@meesho.com</t>
+  </si>
+  <si>
+    <t>tapas.bhuinya@meesho.com</t>
+  </si>
+  <si>
+    <t>umakant.maurya@meesho.com</t>
+  </si>
+  <si>
+    <t>ajeet.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>gurjit.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>sourabh.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>shreyash.kapse@meesho.com</t>
+  </si>
+  <si>
+    <t>shashikant.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>narvin.k@meesho.com</t>
+  </si>
+  <si>
+    <t>prakul.jaret@meesho.com</t>
+  </si>
+  <si>
+    <t>kanhai.thakur@meesho.com</t>
+  </si>
+  <si>
+    <t>ratul.paul@meesho.com</t>
+  </si>
+  <si>
+    <t>pranjit.das@meesho.com</t>
+  </si>
+  <si>
+    <t>Bikash Borah</t>
+  </si>
+  <si>
+    <t>vishal.soni@meesho.com</t>
+  </si>
+  <si>
+    <t>nitesh.mehta@meesho.com</t>
+  </si>
+  <si>
+    <t>trivedi.sureshbhai@meesho.com</t>
+  </si>
+  <si>
+    <t>sanket.pundkar@meesho.com</t>
+  </si>
+  <si>
+    <t>kalal.vinod@meesho.com</t>
+  </si>
+  <si>
+    <t>vishal2@meesho.com</t>
+  </si>
+  <si>
+    <t>shobhit@meesho.com</t>
+  </si>
+  <si>
+    <t>prahalad.jha@meesho.com</t>
+  </si>
+  <si>
+    <t>Vishwas.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>raj.yadav1@meesho.com</t>
+  </si>
+  <si>
+    <t>abir.roy@meesho.com</t>
+  </si>
+  <si>
+    <t>rahul.patil1@meesho.com</t>
+  </si>
+  <si>
+    <t>roshan.asthiya@meesho.com</t>
+  </si>
+  <si>
+    <t>subrata.mondal@meesho.com</t>
+  </si>
+  <si>
+    <t>sonu.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>vinay.bhushan@meesho.com</t>
+  </si>
+  <si>
+    <t>mohammad.rizwan@meesho.com</t>
+  </si>
+  <si>
+    <t>deep.dey@meesho.com</t>
+  </si>
+  <si>
+    <t>dileep.kashyap@meesho.com</t>
+  </si>
+  <si>
+    <t>vikas.prajapat@meesho.com</t>
+  </si>
+  <si>
+    <t>ashok.naik@meesho.com</t>
+  </si>
+  <si>
+    <t>ramesh.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>banti@meesho.com</t>
+  </si>
+  <si>
+    <t>sandeep.chauhan@meesho.com</t>
+  </si>
+  <si>
+    <t>paramjeet.dahiya@meesho.com</t>
+  </si>
+  <si>
+    <t>rana.pratap@meesho.com</t>
+  </si>
+  <si>
+    <t>shankar.dagar@meesho.com</t>
+  </si>
+  <si>
+    <t>vishwajeet.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>praveen.sen@meesho.com</t>
+  </si>
+  <si>
+    <t>sanket.kolhe@meesho.com</t>
+  </si>
+  <si>
+    <t>krishna.pandey@meesho.com</t>
+  </si>
+  <si>
+    <t>akhand.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>nishant.dubey@meesho.com</t>
+  </si>
+  <si>
+    <t>nikesh.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>vikas.kumar2@meesho.com</t>
+  </si>
+  <si>
+    <t>yash.raj1@meesho.com</t>
+  </si>
+  <si>
+    <t>Sagar.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>aslam@meesho.com</t>
+  </si>
+  <si>
+    <t>sachin.dahiya@meesho.com</t>
+  </si>
+  <si>
+    <t>rahul.kumar9@meesho.com</t>
+  </si>
+  <si>
+    <t>pawan.tripathi@meesho.com</t>
+  </si>
+  <si>
+    <t>rushikesh.jadhav@meesho.com</t>
+  </si>
+  <si>
+    <t>minakshi.pundir@meesho.com</t>
+  </si>
+  <si>
+    <t>lokendra.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>hemant.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>sarvan@meesho.com</t>
+  </si>
+  <si>
+    <t>sandeep.char@meesho.com</t>
+  </si>
+  <si>
+    <t>vicky.yadav@meesho.com</t>
+  </si>
+  <si>
+    <t>somenath.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>abhinaba.debnath@meesho.com</t>
+  </si>
+  <si>
+    <t>pramod.behera@meesho.com</t>
+  </si>
+  <si>
+    <t>rajat.sengar@meesho.com</t>
+  </si>
+  <si>
+    <t>chhatrapal.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>vimal.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>roushan.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>abhishek.padmane@meesho.com</t>
+  </si>
+  <si>
+    <t>Shivam.rajput1@meesho.com</t>
+  </si>
+  <si>
+    <t>ojha.ajay@meesho.com</t>
+  </si>
+  <si>
+    <t>santosh.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>neeraj.sharma2@meesho.com</t>
+  </si>
+  <si>
+    <t>ashish.kumar7@meesho.com</t>
+  </si>
+  <si>
+    <t>hari.om1@meesho.com</t>
+  </si>
+  <si>
+    <t>raju.rav@meesho.com</t>
+  </si>
+  <si>
+    <t>sanket.patil1@meesho.com</t>
+  </si>
+  <si>
+    <t>Shubham1@meesho.com</t>
+  </si>
+  <si>
+    <t>upendra.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>arashdeep.singh@meesho.com</t>
+  </si>
+  <si>
+    <t>saurabhkumar.prashad@eesho.com</t>
+  </si>
+  <si>
+    <t>abhiyuddh.soni@meesho.com</t>
+  </si>
+  <si>
+    <t>deepraj.deshmukh@meesho.com</t>
+  </si>
+  <si>
+    <t>dipjyoti.dey@meesho.com</t>
+  </si>
+  <si>
+    <t>pushpendra.patel@meesho.com</t>
+  </si>
+  <si>
+    <t>md.tarafdar@meesho.com</t>
+  </si>
+  <si>
+    <t>akshata.wanve@meesho.com</t>
+  </si>
+  <si>
+    <t>deepak.gupta2@meesho.com</t>
+  </si>
+  <si>
+    <t>joydeep.bagti@meesho.com</t>
+  </si>
+  <si>
+    <t>tanusri.pardhan@meesho.com</t>
+  </si>
+  <si>
+    <t>prabhakar.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>imran.khan2@meesho.com</t>
+  </si>
+  <si>
+    <t>abhijit.mahato@meesho.com</t>
+  </si>
+  <si>
+    <t>chintu.kumar@meesho.com</t>
+  </si>
+  <si>
+    <t>sharad.rathod@meesho.com</t>
+  </si>
+  <si>
+    <t>manoj.kumar3@meesho.com</t>
+  </si>
+  <si>
+    <t>aman.mishra3@meesho.com</t>
+  </si>
+  <si>
+    <t>rohit.chouhan@meesho.com</t>
+  </si>
+  <si>
+    <t>nishant.kumar1@meesho.com</t>
+  </si>
+  <si>
+    <t>saurav.singh1@meesho.com</t>
+  </si>
+  <si>
+    <t>parthiban.p@meesho.com</t>
+  </si>
+  <si>
+    <t>eshant.wasnik@meesho.com</t>
+  </si>
+  <si>
+    <t>vikas.chouhan@meesho.com</t>
+  </si>
+  <si>
+    <t>97301 82936</t>
+  </si>
+  <si>
+    <t>7624961 553</t>
+  </si>
+  <si>
+    <t>97817 67191</t>
+  </si>
+  <si>
+    <t>98600 83678</t>
+  </si>
+  <si>
+    <t>81205 71922</t>
+  </si>
+  <si>
+    <t>6354 324 702</t>
+  </si>
+  <si>
+    <t>87803 55112</t>
+  </si>
+  <si>
+    <t>70032 86129</t>
+  </si>
+  <si>
+    <t>91223 14435</t>
+  </si>
+  <si>
+    <t>6294 048 402</t>
+  </si>
+  <si>
+    <t>81469 33996</t>
+  </si>
+  <si>
+    <t>90071 33024</t>
+  </si>
+  <si>
+    <t>90035 90454</t>
+  </si>
+  <si>
+    <t>Cluster Head</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,13 +1248,84 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF434343"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444746"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF393939"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -349,12 +1356,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -658,7 +1691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E373"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.54296875" bestFit="1" customWidth="1"/>
@@ -696,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>9803091594</v>
@@ -710,10 +1743,10 @@
         <v>8074125321</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>8074125321</v>
@@ -721,16 +1754,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>8129603774</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>8129603774</v>
@@ -738,16 +1771,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>9994448658</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>9994448658</v>
@@ -755,16 +1788,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>9497320464</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6">
         <v>9497320464</v>
@@ -772,16 +1805,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>7358110674</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>7358110674</v>
@@ -789,16 +1822,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>7981901823</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8">
         <v>7981901823</v>
@@ -806,16 +1839,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>6363387963</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9">
         <v>6363387963</v>
@@ -823,16 +1856,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>9666481545</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>9666481545</v>
@@ -840,16 +1873,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>9491229298</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>9491229298</v>
@@ -857,16 +1890,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>8121722331</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>8121722331</v>
@@ -874,16 +1907,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>7794037163</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>7794037163</v>
@@ -891,16 +1924,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>8247226013</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>8247226013</v>
@@ -908,16 +1941,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>6309703197</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15">
         <v>6309703197</v>
@@ -925,16 +1958,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>7981426204</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16">
         <v>7981426204</v>
@@ -942,16 +1975,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>8550010045</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>8550010045</v>
@@ -959,16 +1992,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>9985928248</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18">
         <v>9985928248</v>
@@ -976,16 +2009,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>9966153878</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19">
         <v>9966153878</v>
@@ -993,16 +2026,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>9133204632</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>9133204632</v>
@@ -1010,16 +2043,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>9063456784</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>9063456784</v>
@@ -1027,16 +2060,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>8136801238</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>8136801238</v>
@@ -1044,16 +2077,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>9562942474</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23">
         <v>9562942474</v>
@@ -1061,16 +2094,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>9061229608</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24">
         <v>9061229608</v>
@@ -1078,16 +2111,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>9995305036</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>9995305036</v>
@@ -1095,16 +2128,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>9747474740</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26">
         <v>9747474740</v>
@@ -1112,16 +2145,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>8129392273</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>8129392273</v>
@@ -1129,16 +2162,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>9787039107</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28">
         <v>9787039107</v>
@@ -1146,16 +2179,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>8098698690</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29">
         <v>8098698690</v>
@@ -1163,16 +2196,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>7904028118</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30">
         <v>7904028118</v>
@@ -1180,16 +2213,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31">
         <v>9900549403</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>9900549403</v>
@@ -1197,16 +2230,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>8105466398</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32">
         <v>8105466398</v>
@@ -1214,16 +2247,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>9686649647</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>9686649647</v>
@@ -1231,16 +2264,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>9513666556</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>9513666556</v>
@@ -1248,16 +2281,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>9511785864</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>9511785864</v>
@@ -1265,16 +2298,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36">
         <v>6000981093</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36">
         <v>6000981093</v>
@@ -1282,16 +2315,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37">
         <v>9003590454</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>9003590454</v>
@@ -1299,16 +2332,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38">
         <v>9072731195</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38">
         <v>9072731195</v>
@@ -1316,16 +2349,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39">
         <v>9025995888</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E39">
         <v>9025995888</v>
@@ -1333,16 +2366,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40">
         <v>8825794847</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>8825794847</v>
@@ -1350,16 +2383,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41">
         <v>8883257427</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41">
         <v>8883257427</v>
@@ -1367,16 +2400,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>7867882166</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42">
         <v>7867882166</v>
@@ -1384,16 +2417,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>8668045720</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E43">
         <v>8668045720</v>
@@ -1401,16 +2434,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>8056200304</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E44">
         <v>8056200304</v>
@@ -1418,16 +2451,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>7978549949</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E45">
         <v>7978549949</v>
@@ -1435,16 +2468,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46">
         <v>7077134213</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E46">
         <v>7077134213</v>
@@ -1452,16 +2485,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>7204214516</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E47">
         <v>7204214516</v>
@@ -1469,16 +2502,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>9032477716</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E48">
         <v>9032477716</v>
@@ -1486,16 +2519,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>7889485410</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>7889485410</v>
@@ -1503,16 +2536,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50">
         <v>9164532362</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50">
         <v>9164532362</v>
@@ -1520,16 +2553,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51">
         <v>9035697118</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E51">
         <v>9035697118</v>
@@ -1537,16 +2570,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>7090078440</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E52">
         <v>7090078440</v>
@@ -1554,16 +2587,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>9036661602</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E53">
         <v>9036661602</v>
@@ -1571,16 +2604,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54">
         <v>9663575036</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E54">
         <v>9663575036</v>
@@ -1588,16 +2621,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55">
         <v>7077518998</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E55">
         <v>7077518998</v>
@@ -1605,16 +2638,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56">
         <v>9901443741</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E56">
         <v>9901443741</v>
@@ -1622,16 +2655,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57">
         <v>6381376935</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E57">
         <v>6381376935</v>
@@ -1639,16 +2672,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58">
         <v>9150253325</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58">
         <v>9150253325</v>
@@ -1656,16 +2689,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59">
         <v>6385797985</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E59">
         <v>6385797985</v>
@@ -1673,16 +2706,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60">
         <v>8248754934</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E60">
         <v>8248754934</v>
@@ -1690,16 +2723,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61">
         <v>8754667886</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E61">
         <v>8754667886</v>
@@ -1707,16 +2740,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62">
         <v>9071717181</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E62">
         <v>9071717181</v>
@@ -1724,16 +2757,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63">
         <v>9360681063</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E63">
         <v>9360681063</v>
@@ -1741,16 +2774,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64">
         <v>8660613753</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E64">
         <v>8660613753</v>
@@ -1758,16 +2791,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65">
         <v>8099774097</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E65">
         <v>8099774097</v>
@@ -1775,16 +2808,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66">
         <v>7337008546</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E66">
         <v>7337008546</v>
@@ -1792,16 +2825,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67">
         <v>8309775952</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E67">
         <v>8309775952</v>
@@ -1809,16 +2842,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68">
         <v>8686720525</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68">
         <v>8686720525</v>
@@ -1826,16 +2859,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B69">
         <v>7207708434</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E69">
         <v>7207708434</v>
@@ -1843,16 +2876,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70">
         <v>7013158900</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E70">
         <v>7013158900</v>
@@ -1860,16 +2893,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71">
         <v>9492345130</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E71">
         <v>9492345130</v>
@@ -1877,16 +2910,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B72">
         <v>9966553944</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E72">
         <v>9966553944</v>
@@ -1894,16 +2927,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B73">
         <v>9491120882</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E73">
         <v>9491120882</v>
@@ -1911,24 +2944,5112 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
         <v>82</v>
       </c>
-      <c r="B74" t="s">
+      <c r="D74" t="s">
         <v>80</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75">
+        <v>8007696417</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
         <v>83</v>
       </c>
-      <c r="D74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>85</v>
+      <c r="E75">
+        <v>8007696417</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76">
+        <v>9004551388</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76">
+        <v>9004551388</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77">
+        <v>7001020075</v>
+      </c>
+      <c r="C77" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+      <c r="E77">
+        <v>7001020075</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78">
+        <v>8097928258</v>
+      </c>
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78">
+        <v>8097928258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79">
+        <v>9582713760</v>
+      </c>
+      <c r="C79" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79">
+        <v>9582713760</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80">
+        <v>8591391390</v>
+      </c>
+      <c r="C80" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80">
+        <v>8591391390</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81">
+        <v>8160593572</v>
+      </c>
+      <c r="C81" t="s">
+        <v>398</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81">
+        <v>8160593572</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82">
+        <v>8355872770</v>
+      </c>
+      <c r="C82" t="s">
+        <v>398</v>
+      </c>
+      <c r="D82" t="s">
+        <v>83</v>
+      </c>
+      <c r="E82">
+        <v>8355872770</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83">
+        <v>9969276834</v>
+      </c>
+      <c r="C83" t="s">
+        <v>398</v>
+      </c>
+      <c r="D83" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83">
+        <v>9969276834</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84">
+        <v>7024477807</v>
+      </c>
+      <c r="C84" t="s">
+        <v>398</v>
+      </c>
+      <c r="D84" t="s">
+        <v>83</v>
+      </c>
+      <c r="E84">
+        <v>7024477807</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85">
+        <v>9124377820</v>
+      </c>
+      <c r="C85" t="s">
+        <v>398</v>
+      </c>
+      <c r="D85" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85">
+        <v>9124377820</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86">
+        <v>9166587996</v>
+      </c>
+      <c r="C86" t="s">
+        <v>398</v>
+      </c>
+      <c r="D86" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86">
+        <v>9166587996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87">
+        <v>9212555696</v>
+      </c>
+      <c r="C87" t="s">
+        <v>398</v>
+      </c>
+      <c r="D87" t="s">
+        <v>83</v>
+      </c>
+      <c r="E87">
+        <v>9212555696</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88">
+        <v>9257905437</v>
+      </c>
+      <c r="C88" t="s">
+        <v>398</v>
+      </c>
+      <c r="D88" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88">
+        <v>9257905437</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89">
+        <v>7291972416</v>
+      </c>
+      <c r="C89" t="s">
+        <v>398</v>
+      </c>
+      <c r="D89" t="s">
+        <v>83</v>
+      </c>
+      <c r="E89">
+        <v>7291972416</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90">
+        <v>8527384707</v>
+      </c>
+      <c r="C90" t="s">
+        <v>398</v>
+      </c>
+      <c r="D90" t="s">
+        <v>83</v>
+      </c>
+      <c r="E90">
+        <v>8527384707</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91">
+        <v>6388563799</v>
+      </c>
+      <c r="C91" t="s">
+        <v>398</v>
+      </c>
+      <c r="D91" t="s">
+        <v>83</v>
+      </c>
+      <c r="E91">
+        <v>6388563799</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B92">
+        <v>9266806499</v>
+      </c>
+      <c r="C92" t="s">
+        <v>398</v>
+      </c>
+      <c r="D92" t="s">
+        <v>83</v>
+      </c>
+      <c r="E92">
+        <v>9266806499</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B93">
+        <v>7979735523</v>
+      </c>
+      <c r="C93" t="s">
+        <v>398</v>
+      </c>
+      <c r="D93" t="s">
+        <v>83</v>
+      </c>
+      <c r="E93">
+        <v>7979735523</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B94">
+        <v>6000836880</v>
+      </c>
+      <c r="C94" t="s">
+        <v>398</v>
+      </c>
+      <c r="D94" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94">
+        <v>6000836880</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B95">
+        <v>7001483429</v>
+      </c>
+      <c r="C95" t="s">
+        <v>398</v>
+      </c>
+      <c r="D95" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95">
+        <v>7001483429</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B96">
+        <v>9413978081</v>
+      </c>
+      <c r="C96" t="s">
+        <v>398</v>
+      </c>
+      <c r="D96" t="s">
+        <v>83</v>
+      </c>
+      <c r="E96">
+        <v>9413978081</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B97">
+        <v>8826836418</v>
+      </c>
+      <c r="C97" t="s">
+        <v>398</v>
+      </c>
+      <c r="D97" t="s">
+        <v>83</v>
+      </c>
+      <c r="E97">
+        <v>8826836418</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B98">
+        <v>6393102570</v>
+      </c>
+      <c r="C98" t="s">
+        <v>398</v>
+      </c>
+      <c r="D98" t="s">
+        <v>83</v>
+      </c>
+      <c r="E98">
+        <v>6393102570</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B99">
+        <v>9888665095</v>
+      </c>
+      <c r="C99" t="s">
+        <v>398</v>
+      </c>
+      <c r="D99" t="s">
+        <v>83</v>
+      </c>
+      <c r="E99">
+        <v>9888665095</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B100">
+        <v>9999182731</v>
+      </c>
+      <c r="C100" t="s">
+        <v>398</v>
+      </c>
+      <c r="D100" t="s">
+        <v>83</v>
+      </c>
+      <c r="E100">
+        <v>9999182731</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B101" t="s">
+        <v>385</v>
+      </c>
+      <c r="C101" t="s">
+        <v>398</v>
+      </c>
+      <c r="D101" t="s">
+        <v>83</v>
+      </c>
+      <c r="E101" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B102">
+        <v>7992351620</v>
+      </c>
+      <c r="C102" t="s">
+        <v>398</v>
+      </c>
+      <c r="D102" t="s">
+        <v>83</v>
+      </c>
+      <c r="E102">
+        <v>7992351620</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103">
+        <v>8806659691</v>
+      </c>
+      <c r="C103" t="s">
+        <v>398</v>
+      </c>
+      <c r="D103" t="s">
+        <v>83</v>
+      </c>
+      <c r="E103">
+        <v>8806659691</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B104">
+        <v>7028402715</v>
+      </c>
+      <c r="C104" t="s">
+        <v>398</v>
+      </c>
+      <c r="D104" t="s">
+        <v>83</v>
+      </c>
+      <c r="E104">
+        <v>7028402715</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B105">
+        <v>9303626268</v>
+      </c>
+      <c r="C105" t="s">
+        <v>398</v>
+      </c>
+      <c r="D105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E105">
+        <v>9303626268</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B106">
+        <v>9027246940</v>
+      </c>
+      <c r="C106" t="s">
+        <v>398</v>
+      </c>
+      <c r="D106" t="s">
+        <v>83</v>
+      </c>
+      <c r="E106">
+        <v>9027246940</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B107">
+        <v>7698837388</v>
+      </c>
+      <c r="C107" t="s">
+        <v>398</v>
+      </c>
+      <c r="D107" t="s">
+        <v>83</v>
+      </c>
+      <c r="E107">
+        <v>7698837388</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B108">
+        <v>8930909315</v>
+      </c>
+      <c r="C108" t="s">
+        <v>398</v>
+      </c>
+      <c r="D108" t="s">
+        <v>83</v>
+      </c>
+      <c r="E108">
+        <v>8930909315</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B109">
+        <v>7016450894</v>
+      </c>
+      <c r="C109" t="s">
+        <v>398</v>
+      </c>
+      <c r="D109" t="s">
+        <v>83</v>
+      </c>
+      <c r="E109">
+        <v>7016450894</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B110">
+        <v>9099201055</v>
+      </c>
+      <c r="C110" t="s">
+        <v>398</v>
+      </c>
+      <c r="D110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E110">
+        <v>9099201055</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111">
+        <v>8010417770</v>
+      </c>
+      <c r="C111" t="s">
+        <v>398</v>
+      </c>
+      <c r="D111" t="s">
+        <v>83</v>
+      </c>
+      <c r="E111">
+        <v>8010417770</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B112">
+        <v>9766803981</v>
+      </c>
+      <c r="C112" t="s">
+        <v>398</v>
+      </c>
+      <c r="D112" t="s">
+        <v>83</v>
+      </c>
+      <c r="E112">
+        <v>9766803981</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B113">
+        <v>7500636152</v>
+      </c>
+      <c r="C113" t="s">
+        <v>398</v>
+      </c>
+      <c r="D113" t="s">
+        <v>83</v>
+      </c>
+      <c r="E113">
+        <v>7500636152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114">
+        <v>9871651231</v>
+      </c>
+      <c r="C114" t="s">
+        <v>398</v>
+      </c>
+      <c r="D114" t="s">
+        <v>83</v>
+      </c>
+      <c r="E114">
+        <v>9871651231</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B115">
+        <v>8588041335</v>
+      </c>
+      <c r="C115" t="s">
+        <v>398</v>
+      </c>
+      <c r="D115" t="s">
+        <v>83</v>
+      </c>
+      <c r="E115">
+        <v>8588041335</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116">
+        <v>9546813432</v>
+      </c>
+      <c r="C116" t="s">
+        <v>398</v>
+      </c>
+      <c r="D116" t="s">
+        <v>83</v>
+      </c>
+      <c r="E116">
+        <v>9546813432</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B117">
+        <v>9858705037</v>
+      </c>
+      <c r="C117" t="s">
+        <v>398</v>
+      </c>
+      <c r="D117" t="s">
+        <v>83</v>
+      </c>
+      <c r="E117">
+        <v>9858705037</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118">
+        <v>9712948673</v>
+      </c>
+      <c r="C118" t="s">
+        <v>398</v>
+      </c>
+      <c r="D118" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118">
+        <v>9712948673</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119">
+        <v>9173700204</v>
+      </c>
+      <c r="C119" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119">
+        <v>9173700204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120">
+        <v>8888726472</v>
+      </c>
+      <c r="C120" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" t="s">
+        <v>85</v>
+      </c>
+      <c r="E120">
+        <v>8888726472</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121">
+        <v>7767908097</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121">
+        <v>7767908097</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B122">
+        <v>8591085838</v>
+      </c>
+      <c r="C122" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" t="s">
+        <v>85</v>
+      </c>
+      <c r="E122">
+        <v>8591085838</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B123">
+        <v>8700962598</v>
+      </c>
+      <c r="C123" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" t="s">
+        <v>85</v>
+      </c>
+      <c r="E123">
+        <v>8700962598</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B124">
+        <v>9668843849</v>
+      </c>
+      <c r="C124" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" t="s">
+        <v>85</v>
+      </c>
+      <c r="E124">
+        <v>9668843849</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B125">
+        <v>9451983805</v>
+      </c>
+      <c r="C125" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" t="s">
+        <v>85</v>
+      </c>
+      <c r="E125">
+        <v>9451983805</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B126">
+        <v>6398993379</v>
+      </c>
+      <c r="C126" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" t="s">
+        <v>85</v>
+      </c>
+      <c r="E126">
+        <v>6398993379</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B127">
+        <v>7701835822</v>
+      </c>
+      <c r="C127" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" t="s">
+        <v>85</v>
+      </c>
+      <c r="E127">
+        <v>7701835822</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B128" t="s">
+        <v>386</v>
+      </c>
+      <c r="C128" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" t="s">
+        <v>85</v>
+      </c>
+      <c r="E128" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B129">
+        <v>8234854147</v>
+      </c>
+      <c r="C129" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" t="s">
+        <v>85</v>
+      </c>
+      <c r="E129">
+        <v>8234854147</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B130">
+        <v>8278982239</v>
+      </c>
+      <c r="C130" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" t="s">
+        <v>85</v>
+      </c>
+      <c r="E130">
+        <v>8278982239</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B131">
+        <v>9718167299</v>
+      </c>
+      <c r="C131" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" t="s">
+        <v>85</v>
+      </c>
+      <c r="E131">
+        <v>9718167299</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B132">
+        <v>9570715341</v>
+      </c>
+      <c r="C132" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132">
+        <v>9570715341</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B133">
+        <v>9387469513</v>
+      </c>
+      <c r="C133" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" t="s">
+        <v>85</v>
+      </c>
+      <c r="E133">
+        <v>9387469513</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B134">
+        <v>8486874991</v>
+      </c>
+      <c r="C134" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" t="s">
+        <v>85</v>
+      </c>
+      <c r="E134">
+        <v>8486874991</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B135">
+        <v>7027669312</v>
+      </c>
+      <c r="C135" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" t="s">
+        <v>85</v>
+      </c>
+      <c r="E135">
+        <v>7027669312</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B136">
+        <v>6294745548</v>
+      </c>
+      <c r="C136" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" t="s">
+        <v>85</v>
+      </c>
+      <c r="E136">
+        <v>6294745548</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B137">
+        <v>7378792307</v>
+      </c>
+      <c r="C137" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" t="s">
+        <v>85</v>
+      </c>
+      <c r="E137">
+        <v>7378792307</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B138">
+        <v>8192051386</v>
+      </c>
+      <c r="C138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" t="s">
+        <v>85</v>
+      </c>
+      <c r="E138">
+        <v>8192051386</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B139">
+        <v>6352662236</v>
+      </c>
+      <c r="C139" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" t="s">
+        <v>85</v>
+      </c>
+      <c r="E139">
+        <v>6352662236</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B140">
+        <v>9358389188</v>
+      </c>
+      <c r="C140" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" t="s">
+        <v>85</v>
+      </c>
+      <c r="E140">
+        <v>9358389188</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B141">
+        <v>8952933305</v>
+      </c>
+      <c r="C141" t="s">
+        <v>15</v>
+      </c>
+      <c r="D141" t="s">
+        <v>85</v>
+      </c>
+      <c r="E141">
+        <v>8952933305</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B142">
+        <v>8400863508</v>
+      </c>
+      <c r="C142" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142" t="s">
+        <v>85</v>
+      </c>
+      <c r="E142">
+        <v>8400863508</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B143">
+        <v>8910122638</v>
+      </c>
+      <c r="C143" t="s">
+        <v>15</v>
+      </c>
+      <c r="D143" t="s">
+        <v>85</v>
+      </c>
+      <c r="E143">
+        <v>8910122638</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B144">
+        <v>8922876280</v>
+      </c>
+      <c r="C144" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" t="s">
+        <v>85</v>
+      </c>
+      <c r="E144">
+        <v>8922876280</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B145">
+        <v>8090632265</v>
+      </c>
+      <c r="C145" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" t="s">
+        <v>85</v>
+      </c>
+      <c r="E145">
+        <v>8090632265</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B146">
+        <v>8847290992</v>
+      </c>
+      <c r="C146" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" t="s">
+        <v>85</v>
+      </c>
+      <c r="E146">
+        <v>8847290992</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B147" t="s">
+        <v>387</v>
+      </c>
+      <c r="C147" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" t="s">
+        <v>85</v>
+      </c>
+      <c r="E147" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B148">
+        <v>8708294939</v>
+      </c>
+      <c r="C148" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" t="s">
+        <v>85</v>
+      </c>
+      <c r="E148">
+        <v>8708294939</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B149" t="s">
+        <v>388</v>
+      </c>
+      <c r="C149" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" t="s">
+        <v>85</v>
+      </c>
+      <c r="E149" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B150">
+        <v>9709250151</v>
+      </c>
+      <c r="C150" t="s">
+        <v>15</v>
+      </c>
+      <c r="D150" t="s">
+        <v>85</v>
+      </c>
+      <c r="E150">
+        <v>9709250151</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B151">
+        <v>9243766994</v>
+      </c>
+      <c r="C151" t="s">
+        <v>15</v>
+      </c>
+      <c r="D151" t="s">
+        <v>85</v>
+      </c>
+      <c r="E151">
+        <v>9243766994</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B152">
+        <v>7004987908</v>
+      </c>
+      <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" t="s">
+        <v>85</v>
+      </c>
+      <c r="E152">
+        <v>7004987908</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B153">
+        <v>8415860928</v>
+      </c>
+      <c r="C153" t="s">
+        <v>15</v>
+      </c>
+      <c r="D153" t="s">
+        <v>85</v>
+      </c>
+      <c r="E153">
+        <v>8415860928</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B154">
+        <v>7002876911</v>
+      </c>
+      <c r="C154" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" t="s">
+        <v>85</v>
+      </c>
+      <c r="E154">
+        <v>7002876911</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155">
+        <v>7031340486</v>
+      </c>
+      <c r="C155" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" t="s">
+        <v>85</v>
+      </c>
+      <c r="E155">
+        <v>7031340486</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B156">
+        <v>8285808090</v>
+      </c>
+      <c r="C156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" t="s">
+        <v>85</v>
+      </c>
+      <c r="E156">
+        <v>8285808090</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B157">
+        <v>8426846828</v>
+      </c>
+      <c r="C157" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" t="s">
+        <v>85</v>
+      </c>
+      <c r="E157">
+        <v>8426846828</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A158" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B158">
+        <v>8690056113</v>
+      </c>
+      <c r="C158" t="s">
+        <v>15</v>
+      </c>
+      <c r="D158" t="s">
+        <v>85</v>
+      </c>
+      <c r="E158">
+        <v>8690056113</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A159" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B159">
+        <v>9512281207</v>
+      </c>
+      <c r="C159" t="s">
+        <v>15</v>
+      </c>
+      <c r="D159" t="s">
+        <v>85</v>
+      </c>
+      <c r="E159">
+        <v>9512281207</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A160" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B160">
+        <v>8855915553</v>
+      </c>
+      <c r="C160" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160" t="s">
+        <v>85</v>
+      </c>
+      <c r="E160">
+        <v>8855915553</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A161" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B161">
+        <v>9265430735</v>
+      </c>
+      <c r="C161" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" t="s">
+        <v>85</v>
+      </c>
+      <c r="E161">
+        <v>9265430735</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B162">
+        <v>7990365788</v>
+      </c>
+      <c r="C162" t="s">
+        <v>15</v>
+      </c>
+      <c r="D162" t="s">
+        <v>85</v>
+      </c>
+      <c r="E162">
+        <v>7990365788</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B163">
+        <v>8700445098</v>
+      </c>
+      <c r="C163" t="s">
+        <v>15</v>
+      </c>
+      <c r="D163" t="s">
+        <v>85</v>
+      </c>
+      <c r="E163">
+        <v>8700445098</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A164" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B164">
+        <v>9410016350</v>
+      </c>
+      <c r="C164" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164" t="s">
+        <v>85</v>
+      </c>
+      <c r="E164">
+        <v>9410016350</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A165" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B165">
+        <v>7352052463</v>
+      </c>
+      <c r="C165" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" t="s">
+        <v>85</v>
+      </c>
+      <c r="E165">
+        <v>7352052463</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A166" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B166">
+        <v>9956219816</v>
+      </c>
+      <c r="C166" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" t="s">
+        <v>85</v>
+      </c>
+      <c r="E166">
+        <v>9956219816</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A167" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167" t="s">
+        <v>389</v>
+      </c>
+      <c r="C167" t="s">
+        <v>15</v>
+      </c>
+      <c r="D167" t="s">
+        <v>85</v>
+      </c>
+      <c r="E167" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A168" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B168">
+        <v>8637837758</v>
+      </c>
+      <c r="C168" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168" t="s">
+        <v>85</v>
+      </c>
+      <c r="E168">
+        <v>8637837758</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A169" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B169">
+        <v>7588668369</v>
+      </c>
+      <c r="C169" t="s">
+        <v>15</v>
+      </c>
+      <c r="D169" t="s">
+        <v>85</v>
+      </c>
+      <c r="E169">
+        <v>7588668369</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A170" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B170">
+        <v>8429844413</v>
+      </c>
+      <c r="C170" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" t="s">
+        <v>85</v>
+      </c>
+      <c r="E170">
+        <v>8429844413</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A171" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B171">
+        <v>7278927626</v>
+      </c>
+      <c r="C171" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" t="s">
+        <v>85</v>
+      </c>
+      <c r="E171">
+        <v>7278927626</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A172" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B172">
+        <v>8488823936</v>
+      </c>
+      <c r="C172" t="s">
+        <v>15</v>
+      </c>
+      <c r="D172" t="s">
+        <v>85</v>
+      </c>
+      <c r="E172">
+        <v>8488823936</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A173" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B173">
+        <v>9695640704</v>
+      </c>
+      <c r="C173" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" t="s">
+        <v>85</v>
+      </c>
+      <c r="E173">
+        <v>9695640704</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A174" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B174">
+        <v>9610771514</v>
+      </c>
+      <c r="C174" t="s">
+        <v>15</v>
+      </c>
+      <c r="D174" t="s">
+        <v>85</v>
+      </c>
+      <c r="E174">
+        <v>9610771514</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B175">
+        <v>9997845742</v>
+      </c>
+      <c r="C175" t="s">
+        <v>15</v>
+      </c>
+      <c r="D175" t="s">
+        <v>85</v>
+      </c>
+      <c r="E175">
+        <v>9997845742</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B176">
+        <v>8683813743</v>
+      </c>
+      <c r="C176" t="s">
+        <v>15</v>
+      </c>
+      <c r="D176" t="s">
+        <v>85</v>
+      </c>
+      <c r="E176">
+        <v>8683813743</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A177" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B177">
+        <v>8210748344</v>
+      </c>
+      <c r="C177" t="s">
+        <v>15</v>
+      </c>
+      <c r="D177" t="s">
+        <v>85</v>
+      </c>
+      <c r="E177">
+        <v>8210748344</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B178">
+        <v>9687358442</v>
+      </c>
+      <c r="C178" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" t="s">
+        <v>85</v>
+      </c>
+      <c r="E178">
+        <v>9687358442</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A179" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B179">
+        <v>7449412609</v>
+      </c>
+      <c r="C179" t="s">
+        <v>15</v>
+      </c>
+      <c r="D179" t="s">
+        <v>85</v>
+      </c>
+      <c r="E179">
+        <v>7449412609</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A180" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B180">
+        <v>9670622600</v>
+      </c>
+      <c r="C180" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180" t="s">
+        <v>85</v>
+      </c>
+      <c r="E180">
+        <v>9670622600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A181" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B181" t="s">
+        <v>390</v>
+      </c>
+      <c r="C181" t="s">
+        <v>15</v>
+      </c>
+      <c r="D181" t="s">
+        <v>85</v>
+      </c>
+      <c r="E181" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A182" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B182">
+        <v>9166141184</v>
+      </c>
+      <c r="C182" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182" t="s">
+        <v>85</v>
+      </c>
+      <c r="E182">
+        <v>9166141184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B183">
+        <v>9301184536</v>
+      </c>
+      <c r="C183" t="s">
+        <v>15</v>
+      </c>
+      <c r="D183" t="s">
+        <v>85</v>
+      </c>
+      <c r="E183">
+        <v>9301184536</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A184" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B184">
+        <v>7078460985</v>
+      </c>
+      <c r="C184" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184" t="s">
+        <v>85</v>
+      </c>
+      <c r="E184">
+        <v>7078460985</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A185" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B185" t="s">
+        <v>391</v>
+      </c>
+      <c r="C185" t="s">
+        <v>15</v>
+      </c>
+      <c r="D185" t="s">
+        <v>85</v>
+      </c>
+      <c r="E185" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A186" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B186">
+        <v>9813607710</v>
+      </c>
+      <c r="C186" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" t="s">
+        <v>85</v>
+      </c>
+      <c r="E186">
+        <v>9813607710</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A187" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B187">
+        <v>7202862501</v>
+      </c>
+      <c r="C187" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187" t="s">
+        <v>85</v>
+      </c>
+      <c r="E187">
+        <v>7202862501</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A188" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B188">
+        <v>9420477892</v>
+      </c>
+      <c r="C188" t="s">
+        <v>15</v>
+      </c>
+      <c r="D188" t="s">
+        <v>85</v>
+      </c>
+      <c r="E188">
+        <v>9420477892</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A189" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B189">
+        <v>9136364631</v>
+      </c>
+      <c r="C189" t="s">
+        <v>15</v>
+      </c>
+      <c r="D189" t="s">
+        <v>85</v>
+      </c>
+      <c r="E189">
+        <v>9136364631</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A190" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B190">
+        <v>8924962177</v>
+      </c>
+      <c r="C190" t="s">
+        <v>15</v>
+      </c>
+      <c r="D190" t="s">
+        <v>85</v>
+      </c>
+      <c r="E190">
+        <v>8924962177</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A191" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B191">
+        <v>8439394921</v>
+      </c>
+      <c r="C191" t="s">
+        <v>15</v>
+      </c>
+      <c r="D191" t="s">
+        <v>85</v>
+      </c>
+      <c r="E191">
+        <v>8439394921</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A192" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B192">
+        <v>9588199624</v>
+      </c>
+      <c r="C192" t="s">
+        <v>15</v>
+      </c>
+      <c r="D192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E192">
+        <v>9588199624</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A193" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B193">
+        <v>9519180136</v>
+      </c>
+      <c r="C193" t="s">
+        <v>15</v>
+      </c>
+      <c r="D193" t="s">
+        <v>85</v>
+      </c>
+      <c r="E193">
+        <v>9519180136</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A194" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B194">
+        <v>7984429471</v>
+      </c>
+      <c r="C194" t="s">
+        <v>15</v>
+      </c>
+      <c r="D194" t="s">
+        <v>85</v>
+      </c>
+      <c r="E194">
+        <v>7984429471</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A195" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195">
+        <v>9074396112</v>
+      </c>
+      <c r="C195" t="s">
+        <v>15</v>
+      </c>
+      <c r="D195" t="s">
+        <v>85</v>
+      </c>
+      <c r="E195">
+        <v>9074396112</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A196" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B196">
+        <v>9985928248</v>
+      </c>
+      <c r="C196" t="s">
+        <v>15</v>
+      </c>
+      <c r="D196" t="s">
+        <v>85</v>
+      </c>
+      <c r="E196">
+        <v>9985928248</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A197" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B197">
+        <v>9370641864</v>
+      </c>
+      <c r="C197" t="s">
+        <v>15</v>
+      </c>
+      <c r="D197" t="s">
+        <v>85</v>
+      </c>
+      <c r="E197">
+        <v>9370641864</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B198">
+        <v>9690836794</v>
+      </c>
+      <c r="C198" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" t="s">
+        <v>85</v>
+      </c>
+      <c r="E198">
+        <v>9690836794</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A199" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B199">
+        <v>7452063578</v>
+      </c>
+      <c r="C199" t="s">
+        <v>15</v>
+      </c>
+      <c r="D199" t="s">
+        <v>85</v>
+      </c>
+      <c r="E199">
+        <v>7452063578</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A200" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B200">
+        <v>7899868644</v>
+      </c>
+      <c r="C200" t="s">
+        <v>15</v>
+      </c>
+      <c r="D200" t="s">
+        <v>85</v>
+      </c>
+      <c r="E200">
+        <v>7899868644</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A201" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B201">
+        <v>9168377043</v>
+      </c>
+      <c r="C201" t="s">
+        <v>15</v>
+      </c>
+      <c r="D201" t="s">
+        <v>85</v>
+      </c>
+      <c r="E201">
+        <v>9168377043</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A202" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B202">
+        <v>8949954119</v>
+      </c>
+      <c r="C202" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202" t="s">
+        <v>85</v>
+      </c>
+      <c r="E202">
+        <v>8949954119</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A203" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B203">
+        <v>8901471039</v>
+      </c>
+      <c r="C203" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203" t="s">
+        <v>85</v>
+      </c>
+      <c r="E203">
+        <v>8901471039</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B204">
+        <v>9782937212</v>
+      </c>
+      <c r="C204" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204" t="s">
+        <v>85</v>
+      </c>
+      <c r="E204">
+        <v>9782937212</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A205" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B205">
+        <v>8709632635</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205" t="s">
+        <v>85</v>
+      </c>
+      <c r="E205">
+        <v>8709632635</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A206" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B206">
+        <v>8982981396</v>
+      </c>
+      <c r="C206" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" t="s">
+        <v>85</v>
+      </c>
+      <c r="E206">
+        <v>8982981396</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A207" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B207">
+        <v>8178057683</v>
+      </c>
+      <c r="C207" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207" t="s">
+        <v>85</v>
+      </c>
+      <c r="E207">
+        <v>8178057683</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A208" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B208">
+        <v>8860284670</v>
+      </c>
+      <c r="C208" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208" t="s">
+        <v>85</v>
+      </c>
+      <c r="E208">
+        <v>8860284670</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B209">
+        <v>9990171664</v>
+      </c>
+      <c r="C209" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209" t="s">
+        <v>85</v>
+      </c>
+      <c r="E209">
+        <v>9990171664</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B210">
+        <v>7033787504</v>
+      </c>
+      <c r="C210" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210" t="s">
+        <v>85</v>
+      </c>
+      <c r="E210">
+        <v>7033787504</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B211">
+        <v>8864936545</v>
+      </c>
+      <c r="C211" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211" t="s">
+        <v>85</v>
+      </c>
+      <c r="E211">
+        <v>8864936545</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B212">
+        <v>7340255068</v>
+      </c>
+      <c r="C212" t="s">
+        <v>15</v>
+      </c>
+      <c r="D212" t="s">
+        <v>85</v>
+      </c>
+      <c r="E212">
+        <v>7340255068</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A213" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B213">
+        <v>7027651512</v>
+      </c>
+      <c r="C213" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" t="s">
+        <v>85</v>
+      </c>
+      <c r="E213">
+        <v>7027651512</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A214" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B214">
+        <v>8448244830</v>
+      </c>
+      <c r="C214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214" t="s">
+        <v>85</v>
+      </c>
+      <c r="E214">
+        <v>8448244830</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B215">
+        <v>9987140855</v>
+      </c>
+      <c r="C215" t="s">
+        <v>15</v>
+      </c>
+      <c r="D215" t="s">
+        <v>85</v>
+      </c>
+      <c r="E215">
+        <v>9987140855</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B216">
+        <v>7503379592</v>
+      </c>
+      <c r="C216" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216" t="s">
+        <v>85</v>
+      </c>
+      <c r="E216">
+        <v>7503379592</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B217">
+        <v>8057179470</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" t="s">
+        <v>85</v>
+      </c>
+      <c r="E217">
+        <v>8057179470</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B218">
+        <v>9711746381</v>
+      </c>
+      <c r="C218" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218" t="s">
+        <v>85</v>
+      </c>
+      <c r="E218">
+        <v>9711746381</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B219">
+        <v>9627312707</v>
+      </c>
+      <c r="C219" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219" t="s">
+        <v>85</v>
+      </c>
+      <c r="E219">
+        <v>9627312707</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B220">
+        <v>8509291655</v>
+      </c>
+      <c r="C220" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220" t="s">
+        <v>85</v>
+      </c>
+      <c r="E220">
+        <v>8509291655</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B221">
+        <v>9330433451</v>
+      </c>
+      <c r="C221" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221" t="s">
+        <v>85</v>
+      </c>
+      <c r="E221">
+        <v>9330433451</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B222">
+        <v>9123772371</v>
+      </c>
+      <c r="C222" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" t="s">
+        <v>85</v>
+      </c>
+      <c r="E222">
+        <v>9123772371</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B223">
+        <v>9777620745</v>
+      </c>
+      <c r="C223" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223" t="s">
+        <v>85</v>
+      </c>
+      <c r="E223">
+        <v>9777620745</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B224">
+        <v>8433046869</v>
+      </c>
+      <c r="C224" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" t="s">
+        <v>85</v>
+      </c>
+      <c r="E224">
+        <v>8433046869</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B225">
+        <v>8192050676</v>
+      </c>
+      <c r="C225" t="s">
+        <v>15</v>
+      </c>
+      <c r="D225" t="s">
+        <v>85</v>
+      </c>
+      <c r="E225">
+        <v>8192050676</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A226" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B226">
+        <v>8109234404</v>
+      </c>
+      <c r="C226" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" t="s">
+        <v>85</v>
+      </c>
+      <c r="E226">
+        <v>8109234404</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A227" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B227">
+        <v>7827533548</v>
+      </c>
+      <c r="C227" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227" t="s">
+        <v>85</v>
+      </c>
+      <c r="E227">
+        <v>7827533548</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B228">
+        <v>8726728027</v>
+      </c>
+      <c r="C228" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" t="s">
+        <v>85</v>
+      </c>
+      <c r="E228">
+        <v>8726728027</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A229" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B229">
+        <v>9669575993</v>
+      </c>
+      <c r="C229" t="s">
+        <v>15</v>
+      </c>
+      <c r="D229" t="s">
+        <v>85</v>
+      </c>
+      <c r="E229">
+        <v>9669575993</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A230" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B230">
+        <v>9974555917</v>
+      </c>
+      <c r="C230" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" t="s">
+        <v>85</v>
+      </c>
+      <c r="E230">
+        <v>9974555917</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A231" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B231">
+        <v>8349966315</v>
+      </c>
+      <c r="C231" t="s">
+        <v>15</v>
+      </c>
+      <c r="D231" t="s">
+        <v>85</v>
+      </c>
+      <c r="E231">
+        <v>8349966315</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B232">
+        <v>7321052939</v>
+      </c>
+      <c r="C232" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" t="s">
+        <v>85</v>
+      </c>
+      <c r="E232">
+        <v>7321052939</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B233">
+        <v>7877868720</v>
+      </c>
+      <c r="C233" t="s">
+        <v>15</v>
+      </c>
+      <c r="D233" t="s">
+        <v>85</v>
+      </c>
+      <c r="E233">
+        <v>7877868720</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A234" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B234">
+        <v>8173086829</v>
+      </c>
+      <c r="C234" t="s">
+        <v>15</v>
+      </c>
+      <c r="D234" t="s">
+        <v>85</v>
+      </c>
+      <c r="E234">
+        <v>8173086829</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A235" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B235">
+        <v>7078370856</v>
+      </c>
+      <c r="C235" t="s">
+        <v>15</v>
+      </c>
+      <c r="D235" t="s">
+        <v>85</v>
+      </c>
+      <c r="E235">
+        <v>7078370856</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B236">
+        <v>9898244977</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236" t="s">
+        <v>85</v>
+      </c>
+      <c r="E236">
+        <v>9898244977</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B237">
+        <v>9649306441</v>
+      </c>
+      <c r="C237" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" t="s">
+        <v>85</v>
+      </c>
+      <c r="E237">
+        <v>9649306441</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B238">
+        <v>7900856570</v>
+      </c>
+      <c r="C238" t="s">
+        <v>15</v>
+      </c>
+      <c r="D238" t="s">
+        <v>85</v>
+      </c>
+      <c r="E238">
+        <v>7900856570</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B239">
+        <v>9461045650</v>
+      </c>
+      <c r="C239" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239" t="s">
+        <v>85</v>
+      </c>
+      <c r="E239">
+        <v>9461045650</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B240">
+        <v>6284219612</v>
+      </c>
+      <c r="C240" t="s">
+        <v>15</v>
+      </c>
+      <c r="D240" t="s">
+        <v>85</v>
+      </c>
+      <c r="E240">
+        <v>6284219612</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A241" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B241">
+        <v>9653282698</v>
+      </c>
+      <c r="C241" t="s">
+        <v>15</v>
+      </c>
+      <c r="D241" t="s">
+        <v>85</v>
+      </c>
+      <c r="E241">
+        <v>9653282698</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A242" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B242">
+        <v>9649470393</v>
+      </c>
+      <c r="C242" t="s">
+        <v>15</v>
+      </c>
+      <c r="D242" t="s">
+        <v>85</v>
+      </c>
+      <c r="E242">
+        <v>9649470393</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A243" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B243">
+        <v>8745843744</v>
+      </c>
+      <c r="C243" t="s">
+        <v>15</v>
+      </c>
+      <c r="D243" t="s">
+        <v>85</v>
+      </c>
+      <c r="E243">
+        <v>8745843744</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A244" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B244">
+        <v>8448028290</v>
+      </c>
+      <c r="C244" t="s">
+        <v>15</v>
+      </c>
+      <c r="D244" t="s">
+        <v>85</v>
+      </c>
+      <c r="E244">
+        <v>8448028290</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A245" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B245">
+        <v>8866206371</v>
+      </c>
+      <c r="C245" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" t="s">
+        <v>85</v>
+      </c>
+      <c r="E245">
+        <v>8866206371</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A246" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B246">
+        <v>9021190556</v>
+      </c>
+      <c r="C246" t="s">
+        <v>15</v>
+      </c>
+      <c r="D246" t="s">
+        <v>85</v>
+      </c>
+      <c r="E246">
+        <v>9021190556</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A247" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B247">
+        <v>9923610103</v>
+      </c>
+      <c r="C247" t="s">
+        <v>15</v>
+      </c>
+      <c r="D247" t="s">
+        <v>85</v>
+      </c>
+      <c r="E247">
+        <v>9923610103</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A248" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B248">
+        <v>9301528602</v>
+      </c>
+      <c r="C248" t="s">
+        <v>15</v>
+      </c>
+      <c r="D248" t="s">
+        <v>85</v>
+      </c>
+      <c r="E248">
+        <v>9301528602</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A249" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B249">
+        <v>9898715522</v>
+      </c>
+      <c r="C249" t="s">
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>85</v>
+      </c>
+      <c r="E249">
+        <v>9898715522</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A250" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B250">
+        <v>8160776092</v>
+      </c>
+      <c r="C250" t="s">
+        <v>15</v>
+      </c>
+      <c r="D250" t="s">
+        <v>85</v>
+      </c>
+      <c r="E250">
+        <v>8160776092</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A251" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B251">
+        <v>7738879336</v>
+      </c>
+      <c r="C251" t="s">
+        <v>15</v>
+      </c>
+      <c r="D251" t="s">
+        <v>85</v>
+      </c>
+      <c r="E251">
+        <v>7738879336</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A252" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B252">
+        <v>9922621942</v>
+      </c>
+      <c r="C252" t="s">
+        <v>15</v>
+      </c>
+      <c r="D252" t="s">
+        <v>85</v>
+      </c>
+      <c r="E252">
+        <v>9922621942</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A253" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B253">
+        <v>8483900198</v>
+      </c>
+      <c r="C253" t="s">
+        <v>15</v>
+      </c>
+      <c r="D253" t="s">
+        <v>85</v>
+      </c>
+      <c r="E253">
+        <v>8483900198</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B254">
+        <v>9040877464</v>
+      </c>
+      <c r="C254" t="s">
+        <v>15</v>
+      </c>
+      <c r="D254" t="s">
+        <v>85</v>
+      </c>
+      <c r="E254">
+        <v>9040877464</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A255" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B255">
+        <v>9439315064</v>
+      </c>
+      <c r="C255" t="s">
+        <v>15</v>
+      </c>
+      <c r="D255" t="s">
+        <v>85</v>
+      </c>
+      <c r="E255">
+        <v>9439315064</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A256" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B256">
+        <v>9990061118</v>
+      </c>
+      <c r="C256" t="s">
+        <v>15</v>
+      </c>
+      <c r="D256" t="s">
+        <v>85</v>
+      </c>
+      <c r="E256">
+        <v>9990061118</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A257" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B257">
+        <v>8800304177</v>
+      </c>
+      <c r="C257" t="s">
+        <v>15</v>
+      </c>
+      <c r="D257" t="s">
+        <v>85</v>
+      </c>
+      <c r="E257">
+        <v>8800304177</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B258">
+        <v>7056497596</v>
+      </c>
+      <c r="C258" t="s">
+        <v>15</v>
+      </c>
+      <c r="D258" t="s">
+        <v>85</v>
+      </c>
+      <c r="E258">
+        <v>7056497596</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B259">
+        <v>9811699234</v>
+      </c>
+      <c r="C259" t="s">
+        <v>15</v>
+      </c>
+      <c r="D259" t="s">
+        <v>85</v>
+      </c>
+      <c r="E259">
+        <v>9811699234</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B260">
+        <v>7903508833</v>
+      </c>
+      <c r="C260" t="s">
+        <v>15</v>
+      </c>
+      <c r="D260" t="s">
+        <v>85</v>
+      </c>
+      <c r="E260">
+        <v>7903508833</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B261">
+        <v>8638190824</v>
+      </c>
+      <c r="C261" t="s">
+        <v>15</v>
+      </c>
+      <c r="D261" t="s">
+        <v>85</v>
+      </c>
+      <c r="E261">
+        <v>8638190824</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A262" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B262">
+        <v>8811811385</v>
+      </c>
+      <c r="C262" t="s">
+        <v>15</v>
+      </c>
+      <c r="D262" t="s">
+        <v>85</v>
+      </c>
+      <c r="E262">
+        <v>8811811385</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A263" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B263">
+        <v>8059776160</v>
+      </c>
+      <c r="C263" t="s">
+        <v>15</v>
+      </c>
+      <c r="D263" t="s">
+        <v>85</v>
+      </c>
+      <c r="E263">
+        <v>8059776160</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A264" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B264" t="s">
+        <v>392</v>
+      </c>
+      <c r="C264" t="s">
+        <v>15</v>
+      </c>
+      <c r="D264" t="s">
+        <v>85</v>
+      </c>
+      <c r="E264" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A265" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B265">
+        <v>7999541157</v>
+      </c>
+      <c r="C265" t="s">
+        <v>15</v>
+      </c>
+      <c r="D265" t="s">
+        <v>85</v>
+      </c>
+      <c r="E265">
+        <v>7999541157</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A266" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B266">
+        <v>9650365405</v>
+      </c>
+      <c r="C266" t="s">
+        <v>15</v>
+      </c>
+      <c r="D266" t="s">
+        <v>85</v>
+      </c>
+      <c r="E266">
+        <v>9650365405</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B267">
+        <v>8107269797</v>
+      </c>
+      <c r="C267" t="s">
+        <v>15</v>
+      </c>
+      <c r="D267" t="s">
+        <v>85</v>
+      </c>
+      <c r="E267">
+        <v>8107269797</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B268">
+        <v>9119295841</v>
+      </c>
+      <c r="C268" t="s">
+        <v>15</v>
+      </c>
+      <c r="D268" t="s">
+        <v>85</v>
+      </c>
+      <c r="E268">
+        <v>9119295841</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A269" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B269">
+        <v>9318344671</v>
+      </c>
+      <c r="C269" t="s">
+        <v>15</v>
+      </c>
+      <c r="D269" t="s">
+        <v>85</v>
+      </c>
+      <c r="E269">
+        <v>9318344671</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A270" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B270">
+        <v>9696055700</v>
+      </c>
+      <c r="C270" t="s">
+        <v>15</v>
+      </c>
+      <c r="D270" t="s">
+        <v>85</v>
+      </c>
+      <c r="E270">
+        <v>9696055700</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A271" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B271">
+        <v>8334962355</v>
+      </c>
+      <c r="C271" t="s">
+        <v>15</v>
+      </c>
+      <c r="D271" t="s">
+        <v>85</v>
+      </c>
+      <c r="E271">
+        <v>8334962355</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A272" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B272">
+        <v>8574176858</v>
+      </c>
+      <c r="C272" t="s">
+        <v>15</v>
+      </c>
+      <c r="D272" t="s">
+        <v>85</v>
+      </c>
+      <c r="E272">
+        <v>8574176858</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A273" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B273">
+        <v>7311120913</v>
+      </c>
+      <c r="C273" t="s">
+        <v>15</v>
+      </c>
+      <c r="D273" t="s">
+        <v>85</v>
+      </c>
+      <c r="E273">
+        <v>7311120913</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A274" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B274">
+        <v>9872875565</v>
+      </c>
+      <c r="C274" t="s">
+        <v>15</v>
+      </c>
+      <c r="D274" t="s">
+        <v>85</v>
+      </c>
+      <c r="E274">
+        <v>9872875565</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B275">
+        <v>9888665095</v>
+      </c>
+      <c r="C275" t="s">
+        <v>15</v>
+      </c>
+      <c r="D275" t="s">
+        <v>85</v>
+      </c>
+      <c r="E275">
+        <v>9888665095</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A276" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B276">
+        <v>8329814688</v>
+      </c>
+      <c r="C276" t="s">
+        <v>15</v>
+      </c>
+      <c r="D276" t="s">
+        <v>85</v>
+      </c>
+      <c r="E276">
+        <v>8329814688</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A277" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B277">
+        <v>9798676855</v>
+      </c>
+      <c r="C277" t="s">
+        <v>15</v>
+      </c>
+      <c r="D277" t="s">
+        <v>85</v>
+      </c>
+      <c r="E277">
+        <v>9798676855</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A278" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B278">
+        <v>7875979020</v>
+      </c>
+      <c r="C278" t="s">
+        <v>15</v>
+      </c>
+      <c r="D278" t="s">
+        <v>85</v>
+      </c>
+      <c r="E278">
+        <v>7875979020</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A279" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B279">
+        <v>8626930962</v>
+      </c>
+      <c r="C279" t="s">
+        <v>15</v>
+      </c>
+      <c r="D279" t="s">
+        <v>85</v>
+      </c>
+      <c r="E279">
+        <v>8626930962</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A280" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B280" t="s">
+        <v>393</v>
+      </c>
+      <c r="C280" t="s">
+        <v>15</v>
+      </c>
+      <c r="D280" t="s">
+        <v>85</v>
+      </c>
+      <c r="E280" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A281" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B281">
+        <v>7035845116</v>
+      </c>
+      <c r="C281" t="s">
+        <v>15</v>
+      </c>
+      <c r="D281" t="s">
+        <v>85</v>
+      </c>
+      <c r="E281">
+        <v>7035845116</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B282">
+        <v>7002340731</v>
+      </c>
+      <c r="C282" t="s">
+        <v>15</v>
+      </c>
+      <c r="D282" t="s">
+        <v>85</v>
+      </c>
+      <c r="E282">
+        <v>7002340731</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A283" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B283">
+        <v>8678885974</v>
+      </c>
+      <c r="C283" t="s">
+        <v>15</v>
+      </c>
+      <c r="D283" t="s">
+        <v>85</v>
+      </c>
+      <c r="E283">
+        <v>8678885974</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A284" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B284">
+        <v>9315681948</v>
+      </c>
+      <c r="C284" t="s">
+        <v>15</v>
+      </c>
+      <c r="D284" t="s">
+        <v>85</v>
+      </c>
+      <c r="E284">
+        <v>9315681948</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A285" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B285">
+        <v>6351502235</v>
+      </c>
+      <c r="C285" t="s">
+        <v>15</v>
+      </c>
+      <c r="D285" t="s">
+        <v>85</v>
+      </c>
+      <c r="E285">
+        <v>6351502235</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A286" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B286">
+        <v>9725104037</v>
+      </c>
+      <c r="C286" t="s">
+        <v>15</v>
+      </c>
+      <c r="D286" t="s">
+        <v>85</v>
+      </c>
+      <c r="E286">
+        <v>9725104037</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A287" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B287">
+        <v>9812502061</v>
+      </c>
+      <c r="C287" t="s">
+        <v>15</v>
+      </c>
+      <c r="D287" t="s">
+        <v>85</v>
+      </c>
+      <c r="E287">
+        <v>9812502061</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A288" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B288">
+        <v>9909973188</v>
+      </c>
+      <c r="C288" t="s">
+        <v>15</v>
+      </c>
+      <c r="D288" t="s">
+        <v>85</v>
+      </c>
+      <c r="E288">
+        <v>9909973188</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A289" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B289">
+        <v>9557233383</v>
+      </c>
+      <c r="C289" t="s">
+        <v>15</v>
+      </c>
+      <c r="D289" t="s">
+        <v>85</v>
+      </c>
+      <c r="E289">
+        <v>9557233383</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A290" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B290">
+        <v>7704906394</v>
+      </c>
+      <c r="C290" t="s">
+        <v>15</v>
+      </c>
+      <c r="D290" t="s">
+        <v>85</v>
+      </c>
+      <c r="E290">
+        <v>7704906394</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A291" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B291">
+        <v>8448028290</v>
+      </c>
+      <c r="C291" t="s">
+        <v>15</v>
+      </c>
+      <c r="D291" t="s">
+        <v>85</v>
+      </c>
+      <c r="E291">
+        <v>8448028290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A292" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B292">
+        <v>917880672710</v>
+      </c>
+      <c r="C292" t="s">
+        <v>15</v>
+      </c>
+      <c r="D292" t="s">
+        <v>85</v>
+      </c>
+      <c r="E292">
+        <v>917880672710</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A293" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B293">
+        <v>9926906678</v>
+      </c>
+      <c r="C293" t="s">
+        <v>15</v>
+      </c>
+      <c r="D293" t="s">
+        <v>85</v>
+      </c>
+      <c r="E293">
+        <v>9926906678</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A294" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B294">
+        <v>9681185032</v>
+      </c>
+      <c r="C294" t="s">
+        <v>15</v>
+      </c>
+      <c r="D294" t="s">
+        <v>85</v>
+      </c>
+      <c r="E294">
+        <v>9681185032</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A295" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B295">
+        <v>9284643233</v>
+      </c>
+      <c r="C295" t="s">
+        <v>15</v>
+      </c>
+      <c r="D295" t="s">
+        <v>85</v>
+      </c>
+      <c r="E295">
+        <v>9284643233</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A296" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B296">
+        <v>9009149143</v>
+      </c>
+      <c r="C296" t="s">
+        <v>15</v>
+      </c>
+      <c r="D296" t="s">
+        <v>85</v>
+      </c>
+      <c r="E296">
+        <v>9009149143</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A297" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B297">
+        <v>9635977809</v>
+      </c>
+      <c r="C297" t="s">
+        <v>15</v>
+      </c>
+      <c r="D297" t="s">
+        <v>85</v>
+      </c>
+      <c r="E297">
+        <v>9635977809</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A298" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B298">
+        <v>8818005330</v>
+      </c>
+      <c r="C298" t="s">
+        <v>15</v>
+      </c>
+      <c r="D298" t="s">
+        <v>85</v>
+      </c>
+      <c r="E298">
+        <v>8818005330</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A299" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B299">
+        <v>9334040734</v>
+      </c>
+      <c r="C299" t="s">
+        <v>15</v>
+      </c>
+      <c r="D299" t="s">
+        <v>85</v>
+      </c>
+      <c r="E299">
+        <v>9334040734</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B300">
+        <v>8090384994</v>
+      </c>
+      <c r="C300" t="s">
+        <v>15</v>
+      </c>
+      <c r="D300" t="s">
+        <v>85</v>
+      </c>
+      <c r="E300">
+        <v>8090384994</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A301" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B301">
+        <v>8617772165</v>
+      </c>
+      <c r="C301" t="s">
+        <v>15</v>
+      </c>
+      <c r="D301" t="s">
+        <v>85</v>
+      </c>
+      <c r="E301">
+        <v>8617772165</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B302">
+        <v>7880832095</v>
+      </c>
+      <c r="C302" t="s">
+        <v>15</v>
+      </c>
+      <c r="D302" t="s">
+        <v>85</v>
+      </c>
+      <c r="E302">
+        <v>7880832095</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A303" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B303">
+        <v>6376369461</v>
+      </c>
+      <c r="C303" t="s">
+        <v>15</v>
+      </c>
+      <c r="D303" t="s">
+        <v>85</v>
+      </c>
+      <c r="E303">
+        <v>6376369461</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A304" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B304">
+        <v>9078951868</v>
+      </c>
+      <c r="C304" t="s">
+        <v>15</v>
+      </c>
+      <c r="D304" t="s">
+        <v>85</v>
+      </c>
+      <c r="E304">
+        <v>9078951868</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A305" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B305">
+        <v>9953455434</v>
+      </c>
+      <c r="C305" t="s">
+        <v>15</v>
+      </c>
+      <c r="D305" t="s">
+        <v>85</v>
+      </c>
+      <c r="E305">
+        <v>9953455434</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A306" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B306">
+        <v>9671292423</v>
+      </c>
+      <c r="C306" t="s">
+        <v>15</v>
+      </c>
+      <c r="D306" t="s">
+        <v>85</v>
+      </c>
+      <c r="E306">
+        <v>9671292423</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A307" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B307">
+        <v>9021190556</v>
+      </c>
+      <c r="C307" t="s">
+        <v>15</v>
+      </c>
+      <c r="D307" t="s">
+        <v>85</v>
+      </c>
+      <c r="E307">
+        <v>9021190556</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A308" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B308">
+        <v>9068120449</v>
+      </c>
+      <c r="C308" t="s">
+        <v>15</v>
+      </c>
+      <c r="D308" t="s">
+        <v>85</v>
+      </c>
+      <c r="E308">
+        <v>9068120449</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A309" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B309">
+        <v>6200326458</v>
+      </c>
+      <c r="C309" t="s">
+        <v>15</v>
+      </c>
+      <c r="D309" t="s">
+        <v>85</v>
+      </c>
+      <c r="E309">
+        <v>6200326458</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A310" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B310">
+        <v>9953202277</v>
+      </c>
+      <c r="C310" t="s">
+        <v>15</v>
+      </c>
+      <c r="D310" t="s">
+        <v>85</v>
+      </c>
+      <c r="E310">
+        <v>9953202277</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A311" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B311">
+        <v>9534779078</v>
+      </c>
+      <c r="C311" t="s">
+        <v>15</v>
+      </c>
+      <c r="D311" t="s">
+        <v>85</v>
+      </c>
+      <c r="E311">
+        <v>9534779078</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A312" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B312">
+        <v>6261477094</v>
+      </c>
+      <c r="C312" t="s">
+        <v>15</v>
+      </c>
+      <c r="D312" t="s">
+        <v>85</v>
+      </c>
+      <c r="E312">
+        <v>6261477094</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A313" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B313">
+        <v>8605234465</v>
+      </c>
+      <c r="C313" t="s">
+        <v>15</v>
+      </c>
+      <c r="D313" t="s">
+        <v>85</v>
+      </c>
+      <c r="E313">
+        <v>8605234465</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A314" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B314">
+        <v>8081303457</v>
+      </c>
+      <c r="C314" t="s">
+        <v>15</v>
+      </c>
+      <c r="D314" t="s">
+        <v>85</v>
+      </c>
+      <c r="E314">
+        <v>8081303457</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A315" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B315">
+        <v>6387178996</v>
+      </c>
+      <c r="C315" t="s">
+        <v>15</v>
+      </c>
+      <c r="D315" t="s">
+        <v>85</v>
+      </c>
+      <c r="E315">
+        <v>6387178996</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A316" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B316">
+        <v>8896214274</v>
+      </c>
+      <c r="C316" t="s">
+        <v>15</v>
+      </c>
+      <c r="D316" t="s">
+        <v>85</v>
+      </c>
+      <c r="E316">
+        <v>8896214274</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A317" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B317">
+        <v>7209522397</v>
+      </c>
+      <c r="C317" t="s">
+        <v>15</v>
+      </c>
+      <c r="D317" t="s">
+        <v>85</v>
+      </c>
+      <c r="E317">
+        <v>7209522397</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A318" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B318">
+        <v>8210578186</v>
+      </c>
+      <c r="C318" t="s">
+        <v>15</v>
+      </c>
+      <c r="D318" t="s">
+        <v>85</v>
+      </c>
+      <c r="E318">
+        <v>8210578186</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A319" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B319">
+        <v>9122150297</v>
+      </c>
+      <c r="C319" t="s">
+        <v>15</v>
+      </c>
+      <c r="D319" t="s">
+        <v>85</v>
+      </c>
+      <c r="E319">
+        <v>9122150297</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A320" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B320">
+        <v>6204919495</v>
+      </c>
+      <c r="C320" t="s">
+        <v>15</v>
+      </c>
+      <c r="D320" t="s">
+        <v>85</v>
+      </c>
+      <c r="E320">
+        <v>6204919495</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A321" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B321">
+        <v>9991285034</v>
+      </c>
+      <c r="C321" t="s">
+        <v>15</v>
+      </c>
+      <c r="D321" t="s">
+        <v>85</v>
+      </c>
+      <c r="E321">
+        <v>9991285034</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A322" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B322">
+        <v>9424385431</v>
+      </c>
+      <c r="C322" t="s">
+        <v>15</v>
+      </c>
+      <c r="D322" t="s">
+        <v>85</v>
+      </c>
+      <c r="E322">
+        <v>9424385431</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A323" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B323">
+        <v>8607481761</v>
+      </c>
+      <c r="C323" t="s">
+        <v>15</v>
+      </c>
+      <c r="D323" t="s">
+        <v>85</v>
+      </c>
+      <c r="E323">
+        <v>8607481761</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A324" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B324">
+        <v>9415416798</v>
+      </c>
+      <c r="C324" t="s">
+        <v>15</v>
+      </c>
+      <c r="D324" t="s">
+        <v>85</v>
+      </c>
+      <c r="E324">
+        <v>9415416798</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A325" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B325">
+        <v>9172031435</v>
+      </c>
+      <c r="C325" t="s">
+        <v>15</v>
+      </c>
+      <c r="D325" t="s">
+        <v>85</v>
+      </c>
+      <c r="E325">
+        <v>9172031435</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A326" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B326">
+        <v>9953211378</v>
+      </c>
+      <c r="C326" t="s">
+        <v>15</v>
+      </c>
+      <c r="D326" t="s">
+        <v>85</v>
+      </c>
+      <c r="E326">
+        <v>9953211378</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A327" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B327">
+        <v>8279390701</v>
+      </c>
+      <c r="C327" t="s">
+        <v>15</v>
+      </c>
+      <c r="D327" t="s">
+        <v>85</v>
+      </c>
+      <c r="E327">
+        <v>8279390701</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A328" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B328">
+        <v>9354863679</v>
+      </c>
+      <c r="C328" t="s">
+        <v>15</v>
+      </c>
+      <c r="D328" t="s">
+        <v>85</v>
+      </c>
+      <c r="E328">
+        <v>9354863679</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A329" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B329">
+        <v>9837003067</v>
+      </c>
+      <c r="C329" t="s">
+        <v>15</v>
+      </c>
+      <c r="D329" t="s">
+        <v>85</v>
+      </c>
+      <c r="E329">
+        <v>9837003067</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A330" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B330">
+        <v>7908510116</v>
+      </c>
+      <c r="C330" t="s">
+        <v>15</v>
+      </c>
+      <c r="D330" t="s">
+        <v>85</v>
+      </c>
+      <c r="E330">
+        <v>7908510116</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A331" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B331" t="s">
+        <v>394</v>
+      </c>
+      <c r="C331" t="s">
+        <v>15</v>
+      </c>
+      <c r="D331" t="s">
+        <v>85</v>
+      </c>
+      <c r="E331" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A332" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B332">
+        <v>7908731819</v>
+      </c>
+      <c r="C332" t="s">
+        <v>15</v>
+      </c>
+      <c r="D332" t="s">
+        <v>85</v>
+      </c>
+      <c r="E332">
+        <v>7908731819</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A333" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B333">
+        <v>9674018677</v>
+      </c>
+      <c r="C333" t="s">
+        <v>15</v>
+      </c>
+      <c r="D333" t="s">
+        <v>85</v>
+      </c>
+      <c r="E333">
+        <v>9674018677</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A334" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B334">
+        <v>9937659537</v>
+      </c>
+      <c r="C334" t="s">
+        <v>15</v>
+      </c>
+      <c r="D334" t="s">
+        <v>85</v>
+      </c>
+      <c r="E334">
+        <v>9937659537</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A335" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B335">
+        <v>9999166970</v>
+      </c>
+      <c r="C335" t="s">
+        <v>15</v>
+      </c>
+      <c r="D335" t="s">
+        <v>85</v>
+      </c>
+      <c r="E335">
+        <v>9999166970</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A336" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B336">
+        <v>7017142199</v>
+      </c>
+      <c r="C336" t="s">
+        <v>15</v>
+      </c>
+      <c r="D336" t="s">
+        <v>85</v>
+      </c>
+      <c r="E336">
+        <v>7017142199</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A337" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B337">
+        <v>8795780451</v>
+      </c>
+      <c r="C337" t="s">
+        <v>15</v>
+      </c>
+      <c r="D337" t="s">
+        <v>85</v>
+      </c>
+      <c r="E337">
+        <v>8795780451</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A338" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B338">
+        <v>8825144377</v>
+      </c>
+      <c r="C338" t="s">
+        <v>15</v>
+      </c>
+      <c r="D338" t="s">
+        <v>85</v>
+      </c>
+      <c r="E338">
+        <v>8825144377</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A339" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B339">
+        <v>9637889815</v>
+      </c>
+      <c r="C339" t="s">
+        <v>15</v>
+      </c>
+      <c r="D339" t="s">
+        <v>85</v>
+      </c>
+      <c r="E339">
+        <v>9637889815</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A340" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B340">
+        <v>8532901168</v>
+      </c>
+      <c r="C340" t="s">
+        <v>15</v>
+      </c>
+      <c r="D340" t="s">
+        <v>85</v>
+      </c>
+      <c r="E340">
+        <v>8532901168</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A341" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B341">
+        <v>9724030383</v>
+      </c>
+      <c r="C341" t="s">
+        <v>15</v>
+      </c>
+      <c r="D341" t="s">
+        <v>85</v>
+      </c>
+      <c r="E341">
+        <v>9724030383</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A342" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B342">
+        <v>8299178319</v>
+      </c>
+      <c r="C342" t="s">
+        <v>15</v>
+      </c>
+      <c r="D342" t="s">
+        <v>85</v>
+      </c>
+      <c r="E342">
+        <v>8299178319</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A343" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B343">
+        <v>8950644771</v>
+      </c>
+      <c r="C343" t="s">
+        <v>15</v>
+      </c>
+      <c r="D343" t="s">
+        <v>85</v>
+      </c>
+      <c r="E343">
+        <v>8950644771</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A344" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B344">
+        <v>9507747197</v>
+      </c>
+      <c r="C344" t="s">
+        <v>15</v>
+      </c>
+      <c r="D344" t="s">
+        <v>85</v>
+      </c>
+      <c r="E344">
+        <v>9507747197</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A345" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B345">
+        <v>6393953757</v>
+      </c>
+      <c r="C345" t="s">
+        <v>15</v>
+      </c>
+      <c r="D345" t="s">
+        <v>85</v>
+      </c>
+      <c r="E345">
+        <v>6393953757</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A346" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B346" t="s">
+        <v>395</v>
+      </c>
+      <c r="C346" t="s">
+        <v>15</v>
+      </c>
+      <c r="D346" t="s">
+        <v>85</v>
+      </c>
+      <c r="E346" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A347" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B347">
+        <v>8888947833</v>
+      </c>
+      <c r="C347" t="s">
+        <v>15</v>
+      </c>
+      <c r="D347" t="s">
+        <v>85</v>
+      </c>
+      <c r="E347">
+        <v>8888947833</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A348" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B348">
+        <v>9521734046</v>
+      </c>
+      <c r="C348" t="s">
+        <v>15</v>
+      </c>
+      <c r="D348" t="s">
+        <v>85</v>
+      </c>
+      <c r="E348">
+        <v>9521734046</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A349" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B349">
+        <v>6387278620</v>
+      </c>
+      <c r="C349" t="s">
+        <v>15</v>
+      </c>
+      <c r="D349" t="s">
+        <v>85</v>
+      </c>
+      <c r="E349">
+        <v>6387278620</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A350" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B350">
+        <v>9501875303</v>
+      </c>
+      <c r="C350" t="s">
+        <v>15</v>
+      </c>
+      <c r="D350" t="s">
+        <v>85</v>
+      </c>
+      <c r="E350">
+        <v>9501875303</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A351" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B351">
+        <v>8483900198</v>
+      </c>
+      <c r="C351" t="s">
+        <v>15</v>
+      </c>
+      <c r="D351" t="s">
+        <v>85</v>
+      </c>
+      <c r="E351">
+        <v>8483900198</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A352" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B352">
+        <v>8959620999</v>
+      </c>
+      <c r="C352" t="s">
+        <v>15</v>
+      </c>
+      <c r="D352" t="s">
+        <v>85</v>
+      </c>
+      <c r="E352">
+        <v>8959620999</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A353" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B353">
+        <v>9226395808</v>
+      </c>
+      <c r="C353" t="s">
+        <v>15</v>
+      </c>
+      <c r="D353" t="s">
+        <v>85</v>
+      </c>
+      <c r="E353">
+        <v>9226395808</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A354" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B354">
+        <v>9706785585</v>
+      </c>
+      <c r="C354" t="s">
+        <v>15</v>
+      </c>
+      <c r="D354" t="s">
+        <v>85</v>
+      </c>
+      <c r="E354">
+        <v>9706785585</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A355" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B355">
+        <v>8319900868</v>
+      </c>
+      <c r="C355" t="s">
+        <v>15</v>
+      </c>
+      <c r="D355" t="s">
+        <v>85</v>
+      </c>
+      <c r="E355">
+        <v>8319900868</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A356" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B356">
+        <v>8777826460</v>
+      </c>
+      <c r="C356" t="s">
+        <v>15</v>
+      </c>
+      <c r="D356" t="s">
+        <v>85</v>
+      </c>
+      <c r="E356">
+        <v>8777826460</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A357" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B357">
+        <v>9527375893</v>
+      </c>
+      <c r="C357" t="s">
+        <v>15</v>
+      </c>
+      <c r="D357" t="s">
+        <v>85</v>
+      </c>
+      <c r="E357">
+        <v>9527375893</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A358" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B358">
+        <v>8840618252</v>
+      </c>
+      <c r="C358" t="s">
+        <v>15</v>
+      </c>
+      <c r="D358" t="s">
+        <v>85</v>
+      </c>
+      <c r="E358">
+        <v>8840618252</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A359" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B359">
+        <v>7002141897</v>
+      </c>
+      <c r="C359" t="s">
+        <v>15</v>
+      </c>
+      <c r="D359" t="s">
+        <v>85</v>
+      </c>
+      <c r="E359">
+        <v>7002141897</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A360" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B360">
+        <v>6289797052</v>
+      </c>
+      <c r="C360" t="s">
+        <v>15</v>
+      </c>
+      <c r="D360" t="s">
+        <v>85</v>
+      </c>
+      <c r="E360">
+        <v>6289797052</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A361" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B361">
+        <v>7654669235</v>
+      </c>
+      <c r="C361" t="s">
+        <v>15</v>
+      </c>
+      <c r="D361" t="s">
+        <v>85</v>
+      </c>
+      <c r="E361">
+        <v>7654669235</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A362" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B362">
+        <v>8962798776</v>
+      </c>
+      <c r="C362" t="s">
+        <v>15</v>
+      </c>
+      <c r="D362" t="s">
+        <v>85</v>
+      </c>
+      <c r="E362">
+        <v>8962798776</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A363" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B363" t="s">
+        <v>396</v>
+      </c>
+      <c r="C363" t="s">
+        <v>15</v>
+      </c>
+      <c r="D363" t="s">
+        <v>85</v>
+      </c>
+      <c r="E363" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A364" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B364">
+        <v>7260988849</v>
+      </c>
+      <c r="C364" t="s">
+        <v>15</v>
+      </c>
+      <c r="D364" t="s">
+        <v>85</v>
+      </c>
+      <c r="E364">
+        <v>7260988849</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A365" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B365">
+        <v>7218717822</v>
+      </c>
+      <c r="C365" t="s">
+        <v>15</v>
+      </c>
+      <c r="D365" t="s">
+        <v>85</v>
+      </c>
+      <c r="E365">
+        <v>7218717822</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A366" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B366">
+        <v>8770933174</v>
+      </c>
+      <c r="C366" t="s">
+        <v>15</v>
+      </c>
+      <c r="D366" t="s">
+        <v>85</v>
+      </c>
+      <c r="E366">
+        <v>8770933174</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A367" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B367">
+        <v>6203582866</v>
+      </c>
+      <c r="C367" t="s">
+        <v>15</v>
+      </c>
+      <c r="D367" t="s">
+        <v>85</v>
+      </c>
+      <c r="E367">
+        <v>6203582866</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A368" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B368">
+        <v>8827557496</v>
+      </c>
+      <c r="C368" t="s">
+        <v>15</v>
+      </c>
+      <c r="D368" t="s">
+        <v>85</v>
+      </c>
+      <c r="E368">
+        <v>8827557496</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A369" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B369">
+        <v>9693677858</v>
+      </c>
+      <c r="C369" t="s">
+        <v>15</v>
+      </c>
+      <c r="D369" t="s">
+        <v>85</v>
+      </c>
+      <c r="E369">
+        <v>9693677858</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A370" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B370">
+        <v>9771644442</v>
+      </c>
+      <c r="C370" t="s">
+        <v>15</v>
+      </c>
+      <c r="D370" t="s">
+        <v>85</v>
+      </c>
+      <c r="E370">
+        <v>9771644442</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A371" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B371" t="s">
+        <v>397</v>
+      </c>
+      <c r="C371" t="s">
+        <v>15</v>
+      </c>
+      <c r="D371" t="s">
+        <v>85</v>
+      </c>
+      <c r="E371" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A372" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B372">
+        <v>9860083678</v>
+      </c>
+      <c r="C372" t="s">
+        <v>15</v>
+      </c>
+      <c r="D372" t="s">
+        <v>85</v>
+      </c>
+      <c r="E372">
+        <v>9860083678</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A373" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B373">
+        <v>6265255909</v>
+      </c>
+      <c r="C373" t="s">
+        <v>15</v>
+      </c>
+      <c r="D373" t="s">
+        <v>85</v>
+      </c>
+      <c r="E373">
+        <v>6265255909</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E74" r:id="rId1" xr:uid="{7FE87EC1-E330-43F7-9B47-3F0BDD45BCA0}"/>
+    <hyperlink ref="A130" r:id="rId2" display="mailto:sombir@meesho.com" xr:uid="{7B2D0875-52C6-4B5C-BE95-FED533A7790D}"/>
+    <hyperlink ref="A223" r:id="rId3" display="mailto:pradip.bhoi@meesho.com" xr:uid="{6DD5A2D7-5011-4D4B-8E86-706BB9FB0AF8}"/>
+    <hyperlink ref="A235" r:id="rId4" display="mailto:mukul.goyal@meesho.com" xr:uid="{408532FA-B1C9-42A0-BF72-9DB1B0CBD1EC}"/>
+    <hyperlink ref="A258" r:id="rId5" display="mailto:arvind.yadav@meesho.com" xr:uid="{0AD970C2-8F6B-44CB-94C7-2F108F1730B7}"/>
+    <hyperlink ref="A263" r:id="rId6" display="mailto:sonu.yadav@meesho.com" xr:uid="{66F8F7EF-97FA-4DB9-A791-96986F62200D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
